--- a/exports/data_base_lancar_28_07_2026.xlsx
+++ b/exports/data_base_lancar_28_07_2026.xlsx
@@ -24,9 +24,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -2586,8 +2585,16 @@
       <c r="L5" s="10" t="n"/>
       <c r="M5" s="10" t="n"/>
       <c r="N5" s="10" t="n"/>
-      <c r="O5" s="10" t="n"/>
-      <c r="P5" s="10" t="n"/>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>R74.0</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>R74.0</t>
+        </is>
+      </c>
       <c r="Q5" s="10" t="n"/>
       <c r="R5" s="10" t="n">
         <v>19</v>
@@ -2759,9 +2766,21 @@
       <c r="FE5" s="15" t="n"/>
       <c r="FF5" s="15" t="n"/>
       <c r="FG5" s="15" t="n"/>
-      <c r="FH5" s="35" t="n"/>
-      <c r="FI5" s="35" t="n"/>
-      <c r="FJ5" s="35" t="n"/>
+      <c r="FH5" s="35" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FI5" s="35" t="inlineStr">
+        <is>
+          <t>29/07/2026 22:16:12</t>
+        </is>
+      </c>
+      <c r="FJ5" s="35" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
       <c r="FK5" s="35" t="n"/>
       <c r="FL5" s="16" t="inlineStr">
         <is>
